--- a/forms/trg/Formulir_TRG_tila-techrg.xlsx
+++ b/forms/trg/Formulir_TRG_tila-techrg.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B28)</f>
+        <f>COUNTA(Anggota!B5:B29)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F28)</f>
+        <f>COUNTA(Anggota!F5:F29)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,22 +913,22 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Prof. Ir. M. Iqbal Djawad, M.Sc., Ph.D</t>
+          <t>Dr. Ir. Dody Dharmawan Trijuno, M.App.Sc</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>Environmental Physiology</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Hatchery Management</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -950,17 +950,17 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Ir. Zainuddin, M.Si</t>
+          <t>Prof. Ir. M. Iqbal Djawad, M.Sc., Ph.D</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Nutritional Biochemistry</t>
+          <t>Environmental Physiology</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -987,17 +987,17 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ir. Badraeni, M.P</t>
+          <t>Prof. Dr. Ir. Zainuddin, M.Si</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Water Quality of Aquaculture</t>
+          <t>Nutritional Biochemistry</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
@@ -1024,17 +1024,17 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Dr. Andi Aliah Hidayani, S.Si, M.Si</t>
+          <t>Dr. Ir. Badraeni, M.P</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Fish Genetics and Breeding</t>
+          <t>Water Quality of Aquaculture</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -1046,11 +1046,7 @@
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="12" t="n"/>
       <c r="I8" s="12" t="n"/>
-      <c r="J8" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-4541-5539</t>
-        </is>
-      </c>
+      <c r="J8" s="12" t="n"/>
       <c r="K8" s="12" t="n"/>
       <c r="L8" s="12" t="n"/>
       <c r="M8" s="11" t="inlineStr">
@@ -1065,17 +1061,17 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Dr. Marlina Achmad, S.Pi, M.Si</t>
+          <t>Dr. Andi Aliah Hidayani, S.Si, M.Si</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Aquaculture Biotechnology</t>
+          <t>Fish Genetics and Breeding</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
@@ -1087,7 +1083,11 @@
       <c r="G9" s="12" t="n"/>
       <c r="H9" s="12" t="n"/>
       <c r="I9" s="12" t="n"/>
-      <c r="J9" s="12" t="n"/>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-4541-5539</t>
+        </is>
+      </c>
       <c r="K9" s="12" t="n"/>
       <c r="L9" s="12" t="n"/>
       <c r="M9" s="11" t="inlineStr">
@@ -1102,17 +1102,17 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Dr. Fahrul, S.Pi, M.Si</t>
+          <t>Dr. Marlina Achmad, S.Pi, M.Si</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Fish Handling and Food Safety System</t>
+          <t>Aquaculture Biotechnology</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
@@ -1139,17 +1139,17 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Fatratullah Muhsin, S.Pi., M.Sc.</t>
+          <t>Dr. Fahrul, S.Pi, M.Si</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Fish Nutrition and Reproduction</t>
+          <t>Fish Handling and Food Safety System</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
@@ -1176,17 +1176,17 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Sulaiman Haris, S.Pi., M.Si</t>
+          <t>Muhammad Fatratullah Muhsin, S.Pi., M.Sc.</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Reproduction and Breeding of Marine Organisms</t>
+          <t>Fish Nutrition and Reproduction</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
@@ -1213,22 +1213,22 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Assoc Prof. Dr. Mohamad Farizal Rajemi</t>
+          <t>Sulaiman Haris, S.Pi., M.Si</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Sustainable Manufacturing Process (Food Production)</t>
+          <t>Reproduction and Breeding of Marine Organisms</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Universiti Utara Malaysia</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
@@ -1250,22 +1250,22 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Iman Sudrajat, S.Pi,M.Si</t>
+          <t>Assoc Prof. Dr. Mohamad Farizal Rajemi</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Aquaculture Technology</t>
+          <t>Sustainable Manufacturing Process (Food Production)</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Badan Riset dan Inovasi Nasional (National Research and Innovation Agency)</t>
+          <t>Universiti Utara Malaysia</t>
         </is>
       </c>
       <c r="F14" s="12" t="n"/>
@@ -1287,16 +1287,24 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Magfirah Maulania</t>
+          <t>Iman Sudrajat, S.Pi,M.Si</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="11" t="n"/>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Aquaculture Technology</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>Badan Riset dan Inovasi Nasional (National Research and Innovation Agency)</t>
+        </is>
+      </c>
       <c r="F15" s="12" t="n"/>
       <c r="G15" s="12" t="n"/>
       <c r="H15" s="12" t="n"/>
@@ -1316,12 +1324,12 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Puan Amira Fajriatunnisa</t>
+          <t>Magfirah Maulania</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D16" s="12" t="n"/>
@@ -1343,10 +1351,22 @@
       <c r="A17" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="12" t="n"/>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Puan Amira Fajriatunnisa</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
       <c r="D17" s="12" t="n"/>
-      <c r="E17" s="11" t="n"/>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>Nile Tilapia Research Group is a platform for interdisciplinary collaboration aimed at generating practical solutions in the tilapia aquaculture sector and promoting the diversification of processed tilapia products to support food self-sufficiency and improve community well-being.</t>
+        </is>
+      </c>
       <c r="F17" s="12" t="n"/>
       <c r="G17" s="12" t="n"/>
       <c r="H17" s="12" t="n"/>
@@ -1354,7 +1374,11 @@
       <c r="J17" s="12" t="n"/>
       <c r="K17" s="12" t="n"/>
       <c r="L17" s="12" t="n"/>
-      <c r="M17" s="12" t="n"/>
+      <c r="M17" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -1543,15 +1567,32 @@
       <c r="L28" s="12" t="n"/>
       <c r="M28" s="12" t="n"/>
     </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="12" t="n"/>
+      <c r="C29" s="12" t="n"/>
+      <c r="D29" s="12" t="n"/>
+      <c r="E29" s="11" t="n"/>
+      <c r="F29" s="12" t="n"/>
+      <c r="G29" s="12" t="n"/>
+      <c r="H29" s="12" t="n"/>
+      <c r="I29" s="12" t="n"/>
+      <c r="J29" s="12" t="n"/>
+      <c r="K29" s="12" t="n"/>
+      <c r="L29" s="12" t="n"/>
+      <c r="M29" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
